--- a/graficos/LDA_mejores_diversidad.xlsx
+++ b/graficos/LDA_mejores_diversidad.xlsx
@@ -73,16 +73,31 @@
     <t>orps_lim_dictamen_K4_-</t>
   </si>
   <si>
+    <t>orps_lim_dictamen_K3_-</t>
+  </si>
+  <si>
+    <t>comisión_lim_contenido_K3_-</t>
+  </si>
+  <si>
+    <t>orps_lim_contenido_K3_-</t>
+  </si>
+  <si>
     <t>dictamen_dom</t>
   </si>
   <si>
     <t>comisión_lim_dictamen_dom_K3_-</t>
   </si>
   <si>
-    <t>orps_lim_dictamen_K3_-</t>
-  </si>
-  <si>
-    <t>orps_lim_contenido_K3_-</t>
+    <t>contenido_dom</t>
+  </si>
+  <si>
+    <t>orps_lim_contenido_dom_K3_-</t>
+  </si>
+  <si>
+    <t>comisión</t>
+  </si>
+  <si>
+    <t>comisión_dictamen_K3_-</t>
   </si>
   <si>
     <t>orps</t>
@@ -91,27 +106,12 @@
     <t>orps_dictamen_K3_-</t>
   </si>
   <si>
-    <t>comisión</t>
-  </si>
-  <si>
-    <t>comisión_dictamen_K3_-</t>
-  </si>
-  <si>
-    <t>comisión_lim_contenido_K3_-</t>
-  </si>
-  <si>
-    <t>contenido_dom</t>
-  </si>
-  <si>
-    <t>orps_lim_contenido_dom_K3_-</t>
+    <t>comisión_lim_dictamen_K4_-</t>
   </si>
   <si>
     <t>todos_dictamen_K4_-</t>
   </si>
   <si>
-    <t>comisión_lim_dictamen_K4_-</t>
-  </si>
-  <si>
     <t>comisión_lim_contenido_dom_K5_-</t>
   </si>
   <si>
@@ -130,13 +130,13 @@
     <t>comisión_lim_dictamen_K7_-</t>
   </si>
   <si>
-    <t>denuncia_dom</t>
-  </si>
-  <si>
-    <t>todos_denuncia_dom_K3_-</t>
-  </si>
-  <si>
-    <t>orps_contenido_dom_K3_-</t>
+    <t>comisión_contenido_dom_K3_-</t>
+  </si>
+  <si>
+    <t>antecedentes_dictamen</t>
+  </si>
+  <si>
+    <t>orps_lim_antecedentes_dictamen_K3_-</t>
   </si>
 </sst>
 </file>
@@ -641,42 +641,42 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C5" s="2">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="F5" s="3">
         <v>0.8666666666666667</v>
       </c>
       <c r="G5" s="3">
-        <v>-2.830164137697658</v>
+        <v>-0.6101112654883413</v>
       </c>
       <c r="H5" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I5" s="2">
         <v>28</v>
       </c>
       <c r="J5" s="3">
-        <v>0.3214285714285715</v>
+        <v>0.2142857142857143</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C6" s="2">
         <v>3</v>
@@ -685,22 +685,22 @@
         <v>12</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6" s="3">
         <v>0.8666666666666667</v>
       </c>
       <c r="G6" s="3">
-        <v>-0.6101112654883413</v>
+        <v>-0.8599461624014753</v>
       </c>
       <c r="H6" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I6" s="2">
         <v>28</v>
       </c>
       <c r="J6" s="3">
-        <v>0.2142857142857143</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -717,7 +717,7 @@
         <v>12</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7" s="3">
         <v>0.8666666666666667</v>
@@ -737,74 +737,74 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="2">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="2">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="F8" s="3">
         <v>0.8666666666666667</v>
       </c>
       <c r="G8" s="3">
-        <v>-0.8364519936664546</v>
+        <v>-2.830164137697658</v>
       </c>
       <c r="H8" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I8" s="2">
         <v>28</v>
       </c>
       <c r="J8" s="3">
-        <v>0.2142857142857143</v>
+        <v>0.3214285714285715</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="2">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="F9" s="3">
         <v>0.8666666666666667</v>
       </c>
       <c r="G9" s="3">
-        <v>-0.8364519936664546</v>
+        <v>-0.8028431399530342</v>
       </c>
       <c r="H9" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I9" s="2">
         <v>28</v>
       </c>
       <c r="J9" s="3">
-        <v>0.2142857142857143</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" s="2">
         <v>3</v>
@@ -819,24 +819,24 @@
         <v>0.8666666666666667</v>
       </c>
       <c r="G10" s="3">
-        <v>-0.8599461624014753</v>
+        <v>-0.8364519936664546</v>
       </c>
       <c r="H10" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I10" s="2">
         <v>28</v>
       </c>
       <c r="J10" s="3">
-        <v>0.03571428571428571</v>
+        <v>0.2142857142857143</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C11" s="2">
         <v>3</v>
@@ -851,21 +851,21 @@
         <v>0.8666666666666667</v>
       </c>
       <c r="G11" s="3">
-        <v>-0.8028431399530342</v>
+        <v>-0.8364519936664546</v>
       </c>
       <c r="H11" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I11" s="2">
         <v>28</v>
       </c>
       <c r="J11" s="3">
-        <v>0.03571428571428571</v>
+        <v>0.2142857142857143</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>11</v>
@@ -883,7 +883,7 @@
         <v>0.85</v>
       </c>
       <c r="G12" s="3">
-        <v>-0.6075967604965865</v>
+        <v>-0.9450703546876704</v>
       </c>
       <c r="H12" s="2">
         <v>3</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>11</v>
@@ -915,7 +915,7 @@
         <v>0.85</v>
       </c>
       <c r="G13" s="3">
-        <v>-0.9450703546876704</v>
+        <v>-0.6075967604965865</v>
       </c>
       <c r="H13" s="2">
         <v>3</v>
@@ -932,7 +932,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C14" s="2">
         <v>5</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>11</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>11</v>
@@ -1121,42 +1121,42 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="2">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="C20" s="2">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="F20" s="3">
         <v>0.8</v>
       </c>
       <c r="G20" s="3">
-        <v>-1.247822619770308</v>
+        <v>-0.8229617418685935</v>
       </c>
       <c r="H20" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I20" s="2">
         <v>27</v>
       </c>
       <c r="J20" s="3">
-        <v>0.1851851851851852</v>
+        <v>0.03703703703703703</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
@@ -1171,16 +1171,16 @@
         <v>0.8</v>
       </c>
       <c r="G21" s="3">
-        <v>-0.8229617418685935</v>
+        <v>-0.8144580180067832</v>
       </c>
       <c r="H21" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21" s="2">
         <v>27</v>
       </c>
       <c r="J21" s="3">
-        <v>0.03703703703703703</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
   </sheetData>
